--- a/examples/demo_network.xlsx
+++ b/examples/demo_network.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="332">
   <si>
     <t>序号</t>
   </si>
@@ -684,10 +684,10 @@
     <t>高质量项目源; 长期 LP 关系</t>
   </si>
   <si>
-    <t>目标人物 · 圈内可引荐</t>
-  </si>
-  <si>
-    <t>目标</t>
+    <t>想接触 · 圈内可引荐</t>
+  </si>
+  <si>
+    <t>未联系</t>
   </si>
   <si>
     <t>张磊</t>
@@ -915,10 +915,13 @@
     <t>• 没数据的格留空就行，不要填 `-` `无` `NA`。</t>
   </si>
   <si>
-    <t>2. 关键列：关系类型 ⭐ 新增</t>
-  </si>
-  <si>
-    <t>三选一，决定『你』和此人之间是否建立直接好友关系：</t>
+    <t>2. 关键列：关系类型</t>
+  </si>
+  <si>
+    <t>三选一，决定『你』和此人之间是否建立直接好友关系（**不影响搜索本身**——</t>
+  </si>
+  <si>
+    <t>搜索按相关性排序，任何人都可能是你下次自然语言查询的最佳匹配）：</t>
   </si>
   <si>
     <t>• 留空 / 直接 — 默认。把『可信度』作为 Me→此人的边强度。</t>
@@ -927,13 +930,13 @@
     <t>• 弱认识 — 仅强度 1 的边。点头之交、刚加微信、被介绍认识但未深交。</t>
   </si>
   <si>
-    <t>• 目标   — 你不直接认识此人，但希望被引荐到。系统会通过别人的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          『认识』列推算 2-3 跳的最优引荐路径。Demo 表里</t>
-  </si>
-  <si>
-    <t xml:space="preserve">          沈南鹏/张磊/朱啸虎/雷军/张一鸣/段永平/邱国鹭 都是这种。</t>
+    <t>• 未联系 — 你还没直接联系到此人，但希望被引荐到。系统会通过别人的</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           『认识』列推算 2-3 跳的最优引荐路径。Demo 表里</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           沈南鹏/张磊/朱啸虎/雷军/张一鸣/段永平/邱国鹭 都是这种。</t>
   </si>
   <si>
     <t>3. 关键列：认识</t>
@@ -960,7 +963,7 @@
     <t>• 如果填的人不在表里，导入时会警告并跳过</t>
   </si>
   <si>
-    <t>• ★ 想被引荐到某个『目标』，就在中间人那一行的『认识』里写上目标人物。</t>
+    <t>• ★ 想被引荐到某个『未联系』的人，就在中间人那一行的『认识』里写上他。</t>
   </si>
   <si>
     <t>4. 关键列：公司</t>
@@ -978,7 +981,7 @@
     <t>1-5 分。1 = 认识但不熟；3 = 普通朋友；5 = 核心挚友/铁磁。</t>
   </si>
   <si>
-    <t>对『目标』类型的人填 0 即可（系统忽略）。</t>
+    <t>对『未联系』类型的人填 0 即可（系统忽略）。</t>
   </si>
   <si>
     <t>6. 潜在需求</t>
@@ -3274,7 +3277,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -3340,23 +3343,23 @@
         <v>304</v>
       </c>
     </row>
-    <row r="14" spans="1:1" ht="26" customHeight="1">
-      <c r="A14" s="6" t="s">
+    <row r="14" spans="1:1" ht="22" customHeight="1">
+      <c r="A14" s="7" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="22" customHeight="1">
-      <c r="A15" s="7" t="s">
+    <row r="15" spans="1:1" ht="26" customHeight="1">
+      <c r="A15" s="6" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="22" customHeight="1">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="7" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="22" customHeight="1">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="8" t="s">
         <v>308</v>
       </c>
     </row>
@@ -3385,13 +3388,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="23" spans="1:1" ht="26" customHeight="1">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:1" ht="22" customHeight="1">
+      <c r="A23" s="7" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="22" customHeight="1">
-      <c r="A24" s="7" t="s">
+    <row r="24" spans="1:1" ht="26" customHeight="1">
+      <c r="A24" s="6" t="s">
         <v>315</v>
       </c>
     </row>
@@ -3400,13 +3403,13 @@
         <v>316</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="26" customHeight="1">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:1" ht="22" customHeight="1">
+      <c r="A26" s="7" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="22" customHeight="1">
-      <c r="A27" s="7" t="s">
+    <row r="27" spans="1:1" ht="26" customHeight="1">
+      <c r="A27" s="6" t="s">
         <v>318</v>
       </c>
     </row>
@@ -3415,13 +3418,13 @@
         <v>319</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="26" customHeight="1">
-      <c r="A29" s="6" t="s">
+    <row r="29" spans="1:1" ht="22" customHeight="1">
+      <c r="A29" s="7" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="22" customHeight="1">
-      <c r="A30" s="7" t="s">
+    <row r="30" spans="1:1" ht="26" customHeight="1">
+      <c r="A30" s="6" t="s">
         <v>321</v>
       </c>
     </row>
@@ -3430,13 +3433,13 @@
         <v>322</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="26" customHeight="1">
-      <c r="A32" s="6" t="s">
+    <row r="32" spans="1:1" ht="22" customHeight="1">
+      <c r="A32" s="7" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="22" customHeight="1">
-      <c r="A33" s="7" t="s">
+    <row r="33" spans="1:1" ht="26" customHeight="1">
+      <c r="A33" s="6" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3450,24 +3453,29 @@
         <v>326</v>
       </c>
     </row>
-    <row r="36" spans="1:1" ht="26" customHeight="1">
-      <c r="A36" s="6" t="s">
+    <row r="36" spans="1:1" ht="22" customHeight="1">
+      <c r="A36" s="7" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="22" customHeight="1">
-      <c r="A37" s="7" t="s">
+    <row r="37" spans="1:1" ht="26" customHeight="1">
+      <c r="A37" s="6" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="38" spans="1:1" ht="22" customHeight="1">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="39" spans="1:1" ht="22" customHeight="1">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="8" t="s">
         <v>330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="22" customHeight="1">
+      <c r="A40" s="7" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/examples/demo_network.xlsx
+++ b/examples/demo_network.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="334">
   <si>
     <t>序号</t>
   </si>
@@ -915,25 +915,31 @@
     <t>• 没数据的格留空就行，不要填 `-` `无` `NA`。</t>
   </si>
   <si>
-    <t>2. 关键列：关系类型</t>
-  </si>
-  <si>
-    <t>三选一，决定『你』和此人之间是否建立直接好友关系（**不影响搜索本身**——</t>
+    <t>2. 关键列：关系类型（二态、纯事实）</t>
+  </si>
+  <si>
+    <t>二选一，只描述『我和此人有没有联系上』，**不描述意图**。</t>
+  </si>
+  <si>
+    <t>（『下次想找谁』是 web 端搜索框里那句自然语言决定的，不要在表里预定义谁是『目标』。）</t>
+  </si>
+  <si>
+    <t>**不影响搜索本身**——</t>
   </si>
   <si>
     <t>搜索按相关性排序，任何人都可能是你下次自然语言查询的最佳匹配）：</t>
   </si>
   <si>
-    <t>• 留空 / 直接 — 默认。把『可信度』作为 Me→此人的边强度。</t>
-  </si>
-  <si>
-    <t>• 弱认识 — 仅强度 1 的边。点头之交、刚加微信、被介绍认识但未深交。</t>
-  </si>
-  <si>
-    <t>• 未联系 — 你还没直接联系到此人，但希望被引荐到。系统会通过别人的</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           『认识』列推算 2-3 跳的最优引荐路径。Demo 表里</t>
+    <t>• 留空 / 已联系 — 默认。把『可信度』作为 Me→此人的边强度（1-5，</t>
+  </si>
+  <si>
+    <t xml:space="preserve">                  1 = 点头之交，5 = 核心铁磁）。</t>
+  </si>
+  <si>
+    <t>• 未联系 — 我还没直接联系到此人。系统会通过别人的『认识』列推算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">           2-3 跳的最优引荐路径。Demo 表里</t>
   </si>
   <si>
     <t xml:space="preserve">           沈南鹏/张磊/朱啸虎/雷军/张一鸣/段永平/邱国鹭 都是这种。</t>
@@ -3277,7 +3283,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A40"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -3348,8 +3354,8 @@
         <v>305</v>
       </c>
     </row>
-    <row r="15" spans="1:1" ht="26" customHeight="1">
-      <c r="A15" s="6" t="s">
+    <row r="15" spans="1:1" ht="22" customHeight="1">
+      <c r="A15" s="7" t="s">
         <v>306</v>
       </c>
     </row>
@@ -3358,8 +3364,8 @@
         <v>307</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="22" customHeight="1">
-      <c r="A17" s="8" t="s">
+    <row r="17" spans="1:1" ht="26" customHeight="1">
+      <c r="A17" s="6" t="s">
         <v>308</v>
       </c>
     </row>
@@ -3369,7 +3375,7 @@
       </c>
     </row>
     <row r="19" spans="1:1" ht="22" customHeight="1">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="8" t="s">
         <v>310</v>
       </c>
     </row>
@@ -3393,8 +3399,8 @@
         <v>314</v>
       </c>
     </row>
-    <row r="24" spans="1:1" ht="26" customHeight="1">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:1" ht="22" customHeight="1">
+      <c r="A24" s="7" t="s">
         <v>315</v>
       </c>
     </row>
@@ -3403,13 +3409,13 @@
         <v>316</v>
       </c>
     </row>
-    <row r="26" spans="1:1" ht="22" customHeight="1">
-      <c r="A26" s="7" t="s">
+    <row r="26" spans="1:1" ht="26" customHeight="1">
+      <c r="A26" s="6" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="27" spans="1:1" ht="26" customHeight="1">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:1" ht="22" customHeight="1">
+      <c r="A27" s="7" t="s">
         <v>318</v>
       </c>
     </row>
@@ -3418,13 +3424,13 @@
         <v>319</v>
       </c>
     </row>
-    <row r="29" spans="1:1" ht="22" customHeight="1">
-      <c r="A29" s="7" t="s">
+    <row r="29" spans="1:1" ht="26" customHeight="1">
+      <c r="A29" s="6" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="30" spans="1:1" ht="26" customHeight="1">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:1" ht="22" customHeight="1">
+      <c r="A30" s="7" t="s">
         <v>321</v>
       </c>
     </row>
@@ -3433,13 +3439,13 @@
         <v>322</v>
       </c>
     </row>
-    <row r="32" spans="1:1" ht="22" customHeight="1">
-      <c r="A32" s="7" t="s">
+    <row r="32" spans="1:1" ht="26" customHeight="1">
+      <c r="A32" s="6" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="33" spans="1:1" ht="26" customHeight="1">
-      <c r="A33" s="6" t="s">
+    <row r="33" spans="1:1" ht="22" customHeight="1">
+      <c r="A33" s="7" t="s">
         <v>324</v>
       </c>
     </row>
@@ -3448,8 +3454,8 @@
         <v>325</v>
       </c>
     </row>
-    <row r="35" spans="1:1" ht="22" customHeight="1">
-      <c r="A35" s="7" t="s">
+    <row r="35" spans="1:1" ht="26" customHeight="1">
+      <c r="A35" s="6" t="s">
         <v>326</v>
       </c>
     </row>
@@ -3458,8 +3464,8 @@
         <v>327</v>
       </c>
     </row>
-    <row r="37" spans="1:1" ht="26" customHeight="1">
-      <c r="A37" s="6" t="s">
+    <row r="37" spans="1:1" ht="22" customHeight="1">
+      <c r="A37" s="7" t="s">
         <v>328</v>
       </c>
     </row>
@@ -3468,14 +3474,24 @@
         <v>329</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="22" customHeight="1">
-      <c r="A39" s="8" t="s">
+    <row r="39" spans="1:1" ht="26" customHeight="1">
+      <c r="A39" s="6" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="40" spans="1:1" ht="22" customHeight="1">
       <c r="A40" s="7" t="s">
         <v>331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="22" customHeight="1">
+      <c r="A41" s="8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="22" customHeight="1">
+      <c r="A42" s="7" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>

--- a/examples/demo_network.xlsx
+++ b/examples/demo_network.xlsx
@@ -12,14 +12,14 @@
     <sheet name="说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">联系人!$A$1:$L$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">联系人!$A$1:$K$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="334">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="331">
   <si>
     <t>序号</t>
   </si>
@@ -54,9 +54,6 @@
     <t>备注</t>
   </si>
   <si>
-    <t>关系类型</t>
-  </si>
-  <si>
     <t>周景明</t>
   </si>
   <si>
@@ -687,9 +684,6 @@
     <t>想接触 · 圈内可引荐</t>
   </si>
   <si>
-    <t>未联系</t>
-  </si>
-  <si>
     <t>张磊</t>
   </si>
   <si>
@@ -915,34 +909,40 @@
     <t>• 没数据的格留空就行，不要填 `-` `无` `NA`。</t>
   </si>
   <si>
-    <t>2. 关键列：关系类型（二态、纯事实）</t>
-  </si>
-  <si>
-    <t>二选一，只描述『我和此人有没有联系上』，**不描述意图**。</t>
-  </si>
-  <si>
-    <t>（『下次想找谁』是 web 端搜索框里那句自然语言决定的，不要在表里预定义谁是『目标』。）</t>
-  </si>
-  <si>
-    <t>**不影响搜索本身**——</t>
-  </si>
-  <si>
-    <t>搜索按相关性排序，任何人都可能是你下次自然语言查询的最佳匹配）：</t>
-  </si>
-  <si>
-    <t>• 留空 / 已联系 — 默认。把『可信度』作为 Me→此人的边强度（1-5，</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                  1 = 点头之交，5 = 核心铁磁）。</t>
-  </si>
-  <si>
-    <t>• 未联系 — 我还没直接联系到此人。系统会通过别人的『认识』列推算</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           2-3 跳的最优引荐路径。Demo 表里</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           沈南鹏/张磊/朱啸虎/雷军/张一鸣/段永平/邱国鹭 都是这种。</t>
+    <t>2. 最关键的一列：可信度（0-5，单列承载一切）</t>
+  </si>
+  <si>
+    <t>整张表里**唯一**用来表达「我和这个人的关系」的列，只填一个 0-5 的整数：</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  0 → 未联系：我还没直接接触过此人。系统不建 Me 边；命中时会自动算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       1-3 跳的引荐路径并放在搜索结果的『需要引荐』段。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1 → 点头之交：刚加微信、饭局认识、被介绍认识但没深聊。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3 → 普通朋友。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  5 → 核心铁磁。</t>
+  </si>
+  <si>
+    <t>⚠️ 留空 = 默认 3，所以未联系的人**务必显式填 0**。</t>
+  </si>
+  <si>
+    <t>⚠️ **不要在表里预先标谁是『想接触的目标』**。下次想找谁是 web 端搜索框</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    里那句自然语言决定的，由 LLM 解析意图后从全表（含已联系 + 未联系）一起</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    匹配——任何人都可能是某次查询的最佳匹配。</t>
+  </si>
+  <si>
+    <t>Demo 表里 沈南鹏/张磊/朱啸虎/雷军/张一鸣/段永平/邱国鹭 都是 可信度=0。</t>
   </si>
   <si>
     <t>3. 关键列：认识</t>
@@ -969,7 +969,7 @@
     <t>• 如果填的人不在表里，导入时会警告并跳过</t>
   </si>
   <si>
-    <t>• ★ 想被引荐到某个『未联系』的人，就在中间人那一行的『认识』里写上他。</t>
+    <t>• ★ 想被引荐到某个 可信度=0 的人，就在中间人那一行的『认识』里写上他。</t>
   </si>
   <si>
     <t>4. 关键列：公司</t>
@@ -981,16 +981,7 @@
     <t>如果一个人在多家公司任职，用 `;` 分隔。例：`红杉中国; 某创业公司 董事`</t>
   </si>
   <si>
-    <t>5. 可信度</t>
-  </si>
-  <si>
-    <t>1-5 分。1 = 认识但不熟；3 = 普通朋友；5 = 核心挚友/铁磁。</t>
-  </si>
-  <si>
-    <t>对『未联系』类型的人填 0 即可（系统忽略）。</t>
-  </si>
-  <si>
-    <t>6. 潜在需求</t>
+    <t>5. 潜在需求</t>
   </si>
   <si>
     <t>这个人在找什么。系统会用来做『引荐』—— 你可以介绍 A 给 B 当对方的供给方。</t>
@@ -999,7 +990,7 @@
     <t>示例：`LP 资金; 一级 deal flow`；`合规律所资源`；`GPU 算力`。</t>
   </si>
   <si>
-    <t>7. Sheet「关系」（可选）</t>
+    <t>6. Sheet「关系」（可选）</t>
   </si>
   <si>
     <t>如果某条关系信息很丰富（怎么认识的、频率如何），用 `关系` sheet 更合适。</t>
@@ -1011,7 +1002,7 @@
     <t>频率值：weekly / monthly / quarterly / yearly / rare（留空默认 yearly）</t>
   </si>
   <si>
-    <t>8. 重新导入</t>
+    <t>7. 重新导入</t>
   </si>
   <si>
     <t>改完 Excel 后，在项目根跑：</t>
@@ -1454,7 +1445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -1467,10 +1458,9 @@
     <col min="9" max="9" width="22.7109375" customWidth="1"/>
     <col min="10" max="10" width="56.7109375" customWidth="1"/>
     <col min="11" max="11" width="24.7109375" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1504,1270 +1494,1217 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2" s="2">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="H2" s="2">
         <v>5</v>
       </c>
       <c r="I2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="2"/>
-    </row>
-    <row r="3" spans="1:12">
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" s="2">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="H3" s="2">
         <v>4</v>
       </c>
       <c r="I3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>25</v>
-      </c>
       <c r="K3" s="3"/>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" spans="1:12">
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="H4" s="2">
         <v>4</v>
       </c>
       <c r="I4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>30</v>
-      </c>
       <c r="K4" s="3"/>
-      <c r="L4" s="2"/>
-    </row>
-    <row r="5" spans="1:12">
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>32</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>33</v>
       </c>
       <c r="H5" s="2">
         <v>4</v>
       </c>
       <c r="I5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="K5" s="3"/>
-      <c r="L5" s="2"/>
-    </row>
-    <row r="6" spans="1:12">
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="H6" s="2">
         <v>5</v>
       </c>
       <c r="I6" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="2"/>
-    </row>
-    <row r="7" spans="1:12">
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>46</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="H7" s="2">
         <v>4</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="K7" s="3"/>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12">
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="G8" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="H8" s="2">
         <v>4</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="L8" s="2"/>
-    </row>
-    <row r="9" spans="1:12">
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="F9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>62</v>
       </c>
       <c r="H9" s="2">
         <v>3</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="2"/>
-    </row>
-    <row r="10" spans="1:12">
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" s="2">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="F10" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="H10" s="2">
         <v>4</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L10" s="2"/>
-    </row>
-    <row r="11" spans="1:12">
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" s="2">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>74</v>
       </c>
       <c r="H11" s="2">
         <v>3</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="2"/>
-    </row>
-    <row r="12" spans="1:12">
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12" s="2">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="F12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="H12" s="2">
         <v>4</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="L12" s="2"/>
-    </row>
-    <row r="13" spans="1:12">
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" s="2">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="H13" s="2">
         <v>3</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="L13" s="2"/>
-    </row>
-    <row r="14" spans="1:12">
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" s="2">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="F14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>97</v>
       </c>
       <c r="H14" s="2">
         <v>3</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>99</v>
-      </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="2"/>
-    </row>
-    <row r="15" spans="1:12">
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" s="2">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="F15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="H15" s="2">
         <v>5</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="L15" s="2"/>
-    </row>
-    <row r="16" spans="1:12">
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" s="2">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="H16" s="2">
         <v>4</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="K16" s="3"/>
-      <c r="L16" s="2"/>
-    </row>
-    <row r="17" spans="1:12">
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" s="2">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C17" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G17" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>116</v>
       </c>
       <c r="H17" s="2">
         <v>4</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="K17" s="3"/>
-      <c r="L17" s="2"/>
-    </row>
-    <row r="18" spans="1:12">
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" s="2">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="E18" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="E18" s="3" t="s">
+      <c r="F18" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="H18" s="2">
         <v>3</v>
       </c>
       <c r="I18" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="K18" s="3"/>
-      <c r="L18" s="2"/>
-    </row>
-    <row r="19" spans="1:12">
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" s="2">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C19" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="D19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E19" s="3" t="s">
+      <c r="F19" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>128</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="H19" s="2">
         <v>3</v>
       </c>
       <c r="I19" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="K19" s="3"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" spans="1:12">
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" s="2">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="F20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G20" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="H20" s="2">
         <v>5</v>
       </c>
       <c r="I20" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" spans="1:12">
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" s="2">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="E21" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E21" s="3" t="s">
+      <c r="F21" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="H21" s="2">
         <v>4</v>
       </c>
       <c r="I21" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="L21" s="2"/>
-    </row>
-    <row r="22" spans="1:12">
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" s="2">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="E22" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="E22" s="3" t="s">
+      <c r="F22" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="H22" s="2">
         <v>3</v>
       </c>
       <c r="I22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" spans="1:12">
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" s="2">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="D23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>161</v>
       </c>
       <c r="H23" s="2">
         <v>3</v>
       </c>
       <c r="I23" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>163</v>
-      </c>
       <c r="K23" s="3"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" spans="1:12">
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" s="2">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G24" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>168</v>
       </c>
       <c r="H24" s="2">
         <v>4</v>
       </c>
       <c r="I24" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="K24" s="3"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" spans="1:12">
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" s="2">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="E25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="F25" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>174</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>175</v>
       </c>
       <c r="H25" s="2">
         <v>4</v>
       </c>
       <c r="I25" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="K25" s="3"/>
-      <c r="L25" s="2"/>
-    </row>
-    <row r="26" spans="1:12">
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" s="2">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>182</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>183</v>
       </c>
       <c r="H26" s="2">
         <v>3</v>
       </c>
       <c r="I26" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>185</v>
-      </c>
       <c r="K26" s="3"/>
-      <c r="L26" s="2"/>
-    </row>
-    <row r="27" spans="1:12">
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" s="2">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="E27" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="E27" s="3" t="s">
+      <c r="F27" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G27" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="H27" s="2">
         <v>3</v>
       </c>
       <c r="I27" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>192</v>
-      </c>
       <c r="K27" s="3"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" spans="1:12">
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" s="2">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="F28" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="G28" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="H28" s="2">
         <v>3</v>
       </c>
       <c r="I28" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="J28" s="3" t="s">
-        <v>199</v>
-      </c>
       <c r="K28" s="3"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" spans="1:12">
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" s="2">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="F29" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G29" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="H29" s="2">
         <v>3</v>
       </c>
       <c r="I29" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>206</v>
-      </c>
       <c r="K29" s="3"/>
-      <c r="L29" s="2"/>
-    </row>
-    <row r="30" spans="1:12">
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" s="2">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C30" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="D30" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="F30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="H30" s="2">
         <v>3</v>
       </c>
       <c r="I30" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="K30" s="3"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" spans="1:12">
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" s="4">
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="D31" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="E31" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="H31" s="4">
         <v>0</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
       <c r="A32" s="4">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F32" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>224</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="G32" s="5" t="s">
-        <v>226</v>
       </c>
       <c r="H32" s="4">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" s="4">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="D33" s="5" t="s">
+      <c r="F33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>229</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="5" t="s">
-        <v>231</v>
       </c>
       <c r="H33" s="4">
         <v>0</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" s="4">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D34" s="5" t="s">
+      <c r="F34" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G34" s="5" t="s">
         <v>234</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="5" t="s">
-        <v>236</v>
       </c>
       <c r="H34" s="4">
         <v>0</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" s="4">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="D35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>240</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>242</v>
       </c>
       <c r="H35" s="4">
         <v>0</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" s="4">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="D36" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="E36" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="F36" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="G36" s="5" t="s">
         <v>247</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="G36" s="5" t="s">
-        <v>249</v>
       </c>
       <c r="H36" s="4">
         <v>0</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" s="4">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G37" s="5" t="s">
         <v>251</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="G37" s="5" t="s">
-        <v>253</v>
       </c>
       <c r="H37" s="4">
         <v>0</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L37"/>
+  <autoFilter ref="A1:K37"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2785,495 +2722,495 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>255</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2">
         <v>3</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C3" s="2">
         <v>3</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C4" s="2">
         <v>5</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C5" s="2">
         <v>3</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C6" s="2">
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C7" s="2">
         <v>4</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C9" s="2">
         <v>3</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C10" s="2">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="2">
         <v>3</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C12" s="2">
         <v>3</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C13" s="2">
         <v>3</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C14" s="2">
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C15" s="2">
         <v>3</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C16" s="2">
         <v>3</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C17" s="2">
         <v>3</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2">
         <v>3</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C19" s="2">
         <v>4</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2">
         <v>3</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2">
         <v>3</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C23" s="2">
         <v>4</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2">
         <v>2</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C25" s="2">
         <v>2</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2">
         <v>4</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C28" s="2">
         <v>3</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C29" s="2">
         <v>2</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
@@ -3283,7 +3220,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A42"/>
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="110.7109375" customWidth="1"/>
@@ -3291,207 +3228,202 @@
   <sheetData>
     <row r="1" spans="1:1" ht="30" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="26" customHeight="1">
       <c r="A3" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="22" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="22" customHeight="1">
       <c r="A5" s="7" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:1" ht="22" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:1" ht="26" customHeight="1">
       <c r="A7" s="6" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:1" ht="22" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:1" ht="22" customHeight="1">
       <c r="A9" s="7" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="22" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="11" spans="1:1" ht="22" customHeight="1">
       <c r="A11" s="7" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:1" ht="22" customHeight="1">
       <c r="A12" s="7" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="13" spans="1:1" ht="22" customHeight="1">
       <c r="A13" s="7" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="14" spans="1:1" ht="22" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:1" ht="22" customHeight="1">
       <c r="A15" s="7" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:1" ht="22" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="26" customHeight="1">
-      <c r="A17" s="6" t="s">
-        <v>308</v>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="22" customHeight="1">
+      <c r="A17" s="7" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="18" spans="1:1" ht="22" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" ht="22" customHeight="1">
-      <c r="A19" s="8" t="s">
-        <v>310</v>
+        <v>307</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="26" customHeight="1">
+      <c r="A19" s="6" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="20" spans="1:1" ht="22" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
     </row>
     <row r="21" spans="1:1" ht="22" customHeight="1">
-      <c r="A21" s="7" t="s">
-        <v>312</v>
+      <c r="A21" s="8" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="22" spans="1:1" ht="22" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:1" ht="22" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="1:1" ht="22" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="1:1" ht="22" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" ht="26" customHeight="1">
-      <c r="A26" s="6" t="s">
-        <v>317</v>
+        <v>314</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="22" customHeight="1">
+      <c r="A26" s="7" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:1" ht="22" customHeight="1">
       <c r="A27" s="7" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="26" customHeight="1">
+      <c r="A28" s="6" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="22" customHeight="1">
+      <c r="A29" s="7" t="s">
         <v>318</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" ht="22" customHeight="1">
-      <c r="A28" s="7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" ht="26" customHeight="1">
-      <c r="A29" s="6" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="30" spans="1:1" ht="22" customHeight="1">
       <c r="A30" s="7" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="26" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="22" customHeight="1">
+      <c r="A32" s="7" t="s">
         <v>321</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" ht="22" customHeight="1">
-      <c r="A31" s="7" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" ht="26" customHeight="1">
-      <c r="A32" s="6" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="33" spans="1:1" ht="22" customHeight="1">
       <c r="A33" s="7" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="26" customHeight="1">
+      <c r="A34" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="22" customHeight="1">
+      <c r="A35" s="7" t="s">
         <v>324</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" ht="22" customHeight="1">
-      <c r="A34" s="7" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" ht="26" customHeight="1">
-      <c r="A35" s="6" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="36" spans="1:1" ht="22" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="37" spans="1:1" ht="22" customHeight="1">
       <c r="A37" s="7" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="26" customHeight="1">
+      <c r="A38" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="22" customHeight="1">
+      <c r="A39" s="7" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="38" spans="1:1" ht="22" customHeight="1">
-      <c r="A38" s="7" t="s">
+    <row r="40" spans="1:1" ht="22" customHeight="1">
+      <c r="A40" s="8" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="39" spans="1:1" ht="26" customHeight="1">
-      <c r="A39" s="6" t="s">
+    <row r="41" spans="1:1" ht="22" customHeight="1">
+      <c r="A41" s="7" t="s">
         <v>330</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" ht="22" customHeight="1">
-      <c r="A40" s="7" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" ht="22" customHeight="1">
-      <c r="A41" s="8" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" ht="22" customHeight="1">
-      <c r="A42" s="7" t="s">
-        <v>333</v>
       </c>
     </row>
   </sheetData>
